--- a/main/data/schedule.xlsx
+++ b/main/data/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\project\energetic_site\main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D56196-3DE1-4C76-83B0-F5D2B89F88C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BAF491-44BB-4E4B-8633-6C942F38979C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Апрель 2026" sheetId="4" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Июль 2026" sheetId="7" r:id="rId4"/>
     <sheet name="Август 2026" sheetId="8" r:id="rId5"/>
     <sheet name="Сентябрь 2026" sheetId="9" r:id="rId6"/>
+    <sheet name="Октябрь 2026" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="118">
   <si>
     <t>Название</t>
   </si>
@@ -579,6 +580,267 @@
   </si>
   <si>
     <t>14.09.-18.09.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Электромонтер оперативно-выездной бригады</t>
+  </si>
+  <si>
+    <t>01.10.-05.10.2026</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">01.10.-07.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 01.10.-05.10.26; Практика в УЦ и экзамен 06.10.-07.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>02.10.-13.11.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Теоретический курс в дистанционном формате 02.10.-09.10.26, Производственное обучение на рабочих местах 12.10.-30.10.26,Теоретический курс и Практика в УЦ очный формат 02.11.-11.11.26, КЭ 12.11.-13.11.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>05.10.-15.10.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Теоретический курс в очном формате 05.10.-09.10.26,Теоретический курс дистанционный формат 12.10.-15.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">05.10.-15.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Теоретический курс и  Практика в УЦ очный формат 05.10. -09.10.26; Теоретический курс дистанционный формат 12.10.-15.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>07.10.-28.10.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">  (Теоретический курс в дистанционном формате 07.10.-09.10.26; Производственное обучение на рабочих местах 12.10.-23.10.26, Теоретический курс и Практика в УЦ очный формат 26.10.-27.10.26, КЭ 28.10.2026)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>09.10.-20.11.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Теоретический курс в дистанционном формате 09.10.-16.10.26, Производственное обучение на рабочих местах 19.10.-09.11.26,Теоретический курс и Практика в УЦ очный формат 10.11.-18.11.26, КЭ 19.11-20.11.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>12.10.-16.10.2026</t>
+  </si>
+  <si>
+    <t>12.10.-22.10.2026</t>
+  </si>
+  <si>
+    <t>12.10.-14.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.10.-21.10.2026 </t>
+  </si>
+  <si>
+    <r>
+      <t>16.10.-27.11.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Теоретический курс в дистанционном формате 16.10.-23.10.26, Производственное обучение на рабочих местах 26.10.-16.11.26,Теоретический курс и Практика в УЦ очный формат 17.11.-25.11.26, КЭ 26.11-27.11.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>23.10.-04.12.2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> (Теоретический курс в дистанционном формате 23.10.-30.10.26, Производственное обучение на рабочих местах 02.11.-23.11.26,Теоретический курс и Практика в УЦ очный формат  24.11.-02.12.26, КЭ 03.12.-04.12.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">26.10.-30.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 26.10.-28.10.26; Практика в УЦ и экзамен 29.10.-30.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">05.10.-07.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 05.10.-07.10.26; Практика в УЦ и экзамен 08.10.-09.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">14.10.-15.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате14.10.26; Практика в УЦ и экзамен 15.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">15.10.-30.11.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 15.10.-26.11.26; Практика в УЦ  27.11.-30.11.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">15.10.-16.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 15.10.26; Практика в УЦ и экзамен очный формат 16.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">21.10.-27.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 21.10.-23.10.26; Практика в УЦ и экзамен 26.10.-27.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">28.10-30.10.2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>(Теоретический курс в дистанционном формате 28.10.-29.10.26; Практика в УЦ  30.10.26)</t>
+    </r>
+  </si>
+  <si>
+    <t>Электромонтер по эксплуатации электросчетчиков</t>
+  </si>
+  <si>
+    <t>ПК Диспетчер предприятия электрических сетей</t>
+  </si>
+  <si>
+    <t>Преподаватель  по обучению приемам оказания первой помощи</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Машинист автовышки и автогидроподъемника</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Машинист бурильно-крановой самоходной машины</t>
+  </si>
+  <si>
+    <t>Электромонтер по ремонту воздушных линий электропередачи</t>
   </si>
 </sst>
 </file>
@@ -728,7 +990,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -791,6 +1053,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1923,4 +2188,281 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858E7D9E-1EEC-4317-A47C-E76A7FC8B8F5}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="45.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="66.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>